--- a/demo_data/sectors/toptan_ticaret/mizan_cur.xlsx
+++ b/demo_data/sectors/toptan_ticaret/mizan_cur.xlsx
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>32343.53</v>
+        <v>32343.52</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4245547.95</v>
+        <v>4245547.94</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1157876.71</v>
+        <v>1157876.72</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -1415,7 +1415,7 @@
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>3239849.32</v>
+        <v>3239849.31</v>
       </c>
     </row>
     <row r="56">
@@ -1431,7 +1431,7 @@
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>1951849.32000003</v>
+        <v>1951849.32</v>
       </c>
     </row>
     <row r="57">
